--- a/datasets/sofascore/leagueStats/leagueStats_ITA_2425.xlsx
+++ b/datasets/sofascore/leagueStats/leagueStats_ITA_2425.xlsx
@@ -527,11 +527,11 @@
         <v>0.366972204297787</v>
       </c>
       <c r="H2" t="n">
+        <v>0.4099999964237213</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.4000000059604645</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.4399999976158142</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>1.190574897453187</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I3" t="n">
-        <v>1.399999976158142</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -629,10 +629,10 @@
         <v>0.2058564722538</v>
       </c>
       <c r="H4" t="n">
-        <v>2.970000028610229</v>
+        <v>2.740000009536743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2700000107288361</v>
+        <v>0.300000011920929</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -641,13 +641,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -680,10 +680,10 @@
         <v>0.584606263786564</v>
       </c>
       <c r="H5" t="n">
-        <v>1.129999995231628</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7400000095367432</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -692,13 +692,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="N5" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -731,10 +731,10 @@
         <v>0.979657372459765</v>
       </c>
       <c r="H6" t="n">
-        <v>1.059999942779541</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -782,10 +782,10 @@
         <v>0.2545912051573406</v>
       </c>
       <c r="H7" t="n">
-        <v>1.600000023841858</v>
+        <v>1.470000028610229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3400000035762787</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -833,10 +833,10 @@
         <v>0.6341380197554879</v>
       </c>
       <c r="H8" t="n">
-        <v>2.269999980926514</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N8" t="n">
         <v>0.29</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.65</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
@@ -884,10 +884,10 @@
         <v>0.6203230433165969</v>
       </c>
       <c r="H9" t="n">
-        <v>2.240000009536743</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -896,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -935,7 +935,7 @@
         <v>0.5552877597510841</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I10" t="n">
         <v>0.7799999713897705</v>
@@ -947,13 +947,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="N10" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1.840000033378601</v>
       </c>
       <c r="I11" t="n">
-        <v>1.200000047683716</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="M11" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
@@ -1037,10 +1037,10 @@
         <v>1.322996933051945</v>
       </c>
       <c r="H12" t="n">
-        <v>1.659999966621399</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1088,10 +1088,10 @@
         <v>1.845729393884552</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5899999737739563</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="N13" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1139,10 +1139,10 @@
         <v>0.6944098696112641</v>
       </c>
       <c r="H14" t="n">
-        <v>1.029999971389771</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="I14" t="n">
-        <v>1.080000042915344</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1151,13 +1151,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="N14" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1190,10 +1190,10 @@
         <v>0.808917406946417</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="I15" t="n">
-        <v>1.220000028610229</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="N15" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -1241,10 +1241,10 @@
         <v>0.7840883890166908</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5400000214576721</v>
+        <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.039999961853027</v>
+        <v>0.9900000095367432</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="M16" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="N16" t="n">
         <v>0.27</v>
@@ -1292,10 +1292,10 @@
         <v>0.5345100024715079</v>
       </c>
       <c r="H17" t="n">
-        <v>1.899999976158142</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1304,13 +1304,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="I19" t="n">
-        <v>1.690000057220459</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1409,10 +1409,10 @@
         <v>0.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1445,10 +1445,10 @@
         <v>1.211980643720921</v>
       </c>
       <c r="H20" t="n">
-        <v>2.240000009536743</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="M20" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1496,10 +1496,10 @@
         <v>0.9153891578316742</v>
       </c>
       <c r="H21" t="n">
-        <v>2.759999990463257</v>
+        <v>2.640000104904175</v>
       </c>
       <c r="I21" t="n">
-        <v>1.090000033378601</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="N21" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
@@ -1547,10 +1547,10 @@
         <v>2.000413861125723</v>
       </c>
       <c r="H22" t="n">
-        <v>1.389999985694885</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="I22" t="n">
-        <v>1.720000028610229</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="M22" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -1598,7 +1598,7 @@
         <v>0.8925102129578599</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.75</v>
       </c>
       <c r="I23" t="n">
         <v>1.25</v>
@@ -1610,13 +1610,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="O23" t="n">
         <v>7</v>
@@ -1649,28 +1649,28 @@
         <v>3.340232169294357</v>
       </c>
       <c r="H24" t="n">
-        <v>2.299999952316284</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I24" t="n">
-        <v>2.150000095367432</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1700,10 +1700,10 @@
         <v>0.58408033195883</v>
       </c>
       <c r="H25" t="n">
-        <v>1.529999971389771</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7300000190734863</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="M25" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="N25" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1751,10 +1751,10 @@
         <v>0.467677537351848</v>
       </c>
       <c r="H26" t="n">
-        <v>2.109999895095825</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1763,13 +1763,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -1802,10 +1802,10 @@
         <v>1.055792904458942</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="I27" t="n">
-        <v>1.169999957084656</v>
+        <v>1.320000052452087</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1814,13 +1814,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="M27" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1853,10 +1853,10 @@
         <v>0.7686285953968711</v>
       </c>
       <c r="H28" t="n">
-        <v>1.080000042915344</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="M28" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="N28" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1904,10 +1904,10 @@
         <v>0.17564207315445</v>
       </c>
       <c r="H29" t="n">
-        <v>1.210000038146973</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3899999856948853</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M29" t="n">
         <v>0.21</v>
       </c>
-      <c r="M29" t="n">
-        <v>0.23</v>
-      </c>
       <c r="N29" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -1955,10 +1955,10 @@
         <v>0.242392080835997</v>
       </c>
       <c r="H30" t="n">
-        <v>1.259999990463257</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2899999916553497</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>2.820676051080214</v>
       </c>
       <c r="H31" t="n">
-        <v>1.740000009536743</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I31" t="n">
         <v>1.940000057220459</v>
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="M31" t="n">
         <v>0.88</v>
       </c>
       <c r="N31" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -2057,10 +2057,10 @@
         <v>2.241758786180613</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="I32" t="n">
-        <v>1.190000057220459</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2069,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="M32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -2108,10 +2108,10 @@
         <v>0.5463900938630171</v>
       </c>
       <c r="H33" t="n">
-        <v>1.120000004768372</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7200000286102295</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2120,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M33" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="N33" t="n">
         <v>0.64</v>
@@ -2159,10 +2159,10 @@
         <v>0.469316408038134</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6299999952316284</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="N34" t="n">
         <v>0.99</v>
@@ -2210,10 +2210,10 @@
         <v>1.436876029707489</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4099999964237213</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I35" t="n">
-        <v>1.580000042915344</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2222,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M35" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="N35" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2261,10 +2261,10 @@
         <v>1.157456154003741</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.7900000214576721</v>
       </c>
       <c r="I36" t="n">
-        <v>1.419999957084656</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="M36" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="N36" t="n">
-        <v>0.39</v>
+        <v>0.57</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -2312,10 +2312,10 @@
         <v>0.8419117387384211</v>
       </c>
       <c r="H37" t="n">
-        <v>0.119999997317791</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="I37" t="n">
-        <v>1.350000023841858</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2327,10 +2327,10 @@
         <v>0.01</v>
       </c>
       <c r="M37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N37" t="n">
         <v>0.51</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.52</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>1.662507569417363</v>
       </c>
       <c r="H38" t="n">
-        <v>0.699999988079071</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="I38" t="n">
-        <v>1.409999966621399</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2375,13 +2375,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="N38" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -2414,10 +2414,10 @@
         <v>1.24610170163215</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6299999952316284</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="I39" t="n">
-        <v>1.279999971389771</v>
+        <v>1.25</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2426,13 +2426,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -2465,10 +2465,10 @@
         <v>0.9057432082481669</v>
       </c>
       <c r="H40" t="n">
-        <v>2.049999952316284</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5299999713897705</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2477,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="M40" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="N40" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -2516,10 +2516,10 @@
         <v>2.658684599252054</v>
       </c>
       <c r="H41" t="n">
-        <v>1.799999952316284</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I41" t="n">
-        <v>1.570000052452087</v>
+        <v>1.419999957084656</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="M41" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="N41" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="O41" t="n">
         <v>5</v>
@@ -2567,10 +2567,10 @@
         <v>0.388590551912783</v>
       </c>
       <c r="H42" t="n">
-        <v>1.090000033378601</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I42" t="n">
-        <v>0.449999988079071</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2579,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="M42" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="N42" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -2618,10 +2618,10 @@
         <v>0.7345569971948871</v>
       </c>
       <c r="H43" t="n">
-        <v>1.539999961853027</v>
+        <v>1.610000014305115</v>
       </c>
       <c r="I43" t="n">
-        <v>1.070000052452087</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2630,13 +2630,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="M43" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="N43" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
@@ -2669,7 +2669,7 @@
         <v>2.816640047356498</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2800000011920929</v>
+        <v>0.2899999916553497</v>
       </c>
       <c r="I44" t="n">
         <v>2.200000047683716</v>
@@ -2681,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="M44" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="N44" t="n">
         <v>0.75</v>
@@ -2720,10 +2720,10 @@
         <v>1.463257660157972</v>
       </c>
       <c r="H45" t="n">
-        <v>1.139999985694885</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I45" t="n">
-        <v>1.129999995231628</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2732,13 +2732,13 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="M45" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="N45" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="O45" t="n">
         <v>3</v>
@@ -2774,25 +2774,25 @@
         <v>0.6700000166893005</v>
       </c>
       <c r="I46" t="n">
-        <v>1.220000028610229</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0.28</v>
       </c>
       <c r="M46" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2822,10 +2822,10 @@
         <v>0.893702700734142</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I47" t="n">
-        <v>1.370000004768372</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0.19</v>
       </c>
       <c r="M47" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -2873,28 +2873,28 @@
         <v>1.373256826812025</v>
       </c>
       <c r="H48" t="n">
-        <v>1.460000038146973</v>
+        <v>1.419999957084656</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="N48" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -2924,10 +2924,10 @@
         <v>2.958827722856397</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7300000190734863</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I49" t="n">
-        <v>2.079999923706055</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2936,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="M49" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="N49" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -3026,10 +3026,10 @@
         <v>1.155939042102552</v>
       </c>
       <c r="H51" t="n">
-        <v>1.210000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I51" t="n">
-        <v>2.599999904632568</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3038,13 +3038,13 @@
         <v>2</v>
       </c>
       <c r="L51" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="M51" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="N51" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -3077,10 +3077,10 @@
         <v>2.382413446010646</v>
       </c>
       <c r="H52" t="n">
-        <v>1.269999980926514</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I52" t="n">
-        <v>1.299999952316284</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3092,10 +3092,10 @@
         <v>0.48</v>
       </c>
       <c r="M52" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="N52" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -3128,10 +3128,10 @@
         <v>1.778500117361556</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5699999928474426</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="I53" t="n">
-        <v>1.570000052452087</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3140,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="M53" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="N53" t="n">
         <v>0.89</v>
@@ -3179,10 +3179,10 @@
         <v>0.498057023622089</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6499999761581421</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3799999952316284</v>
+        <v>0.3899999856948853</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3191,13 +3191,13 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M54" t="n">
         <v>0.11</v>
       </c>
       <c r="N54" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -3230,10 +3230,10 @@
         <v>0.642979387193917</v>
       </c>
       <c r="H55" t="n">
-        <v>2.950000047683716</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5600000023841858</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="O55" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
         <v>1.327624395489692</v>
       </c>
       <c r="H56" t="n">
-        <v>1.299999952316284</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I56" t="n">
         <v>0.8700000047683716</v>
@@ -3293,13 +3293,13 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="M56" t="n">
         <v>0.46</v>
       </c>
       <c r="N56" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O56" t="n">
         <v>2</v>
@@ -3332,10 +3332,10 @@
         <v>0.9644117457792131</v>
       </c>
       <c r="H57" t="n">
-        <v>2.400000095367432</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3344,13 +3344,13 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="M57" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="N57" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="O57" t="n">
         <v>2</v>
@@ -3383,10 +3383,10 @@
         <v>0.029028173536063</v>
       </c>
       <c r="H58" t="n">
-        <v>3.130000114440918</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1000000014901161</v>
+        <v>0.09000000357627869</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N58" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
@@ -3434,10 +3434,10 @@
         <v>1.420204349793494</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8600000143051147</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="I59" t="n">
-        <v>1.330000042915344</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="M59" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="N59" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
@@ -3485,10 +3485,10 @@
         <v>0.3700865386053936</v>
       </c>
       <c r="H60" t="n">
-        <v>1.649999976158142</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3497,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="M60" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N60" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="O60" t="n">
         <v>3</v>
@@ -3536,10 +3536,10 @@
         <v>1.766981694886091</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9900000095367432</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I61" t="n">
-        <v>1.240000009536743</v>
+        <v>1.25</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3548,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="M61" t="n">
         <v>0.52</v>
       </c>
       <c r="N61" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         <v>0.428712173365053</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.7099999785423279</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3599,13 +3599,13 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="M62" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="N62" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -3638,10 +3638,10 @@
         <v>1.545127737335857</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="I63" t="n">
-        <v>1.509999990463257</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3650,13 +3650,13 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="M63" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="N63" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -3689,28 +3689,28 @@
         <v>2.064039519056678</v>
       </c>
       <c r="H64" t="n">
-        <v>1.470000028610229</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I64" t="n">
-        <v>1.990000009536743</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="M64" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="N64" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3743,7 +3743,7 @@
         <v>1.320000052452087</v>
       </c>
       <c r="I65" t="n">
-        <v>1.049999952316284</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3755,10 +3755,10 @@
         <v>0.03</v>
       </c>
       <c r="M65" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="N65" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -3791,10 +3791,10 @@
         <v>0.8837895896285709</v>
       </c>
       <c r="H66" t="n">
-        <v>1.100000023841858</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I66" t="n">
-        <v>1.129999995231628</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3803,13 +3803,13 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="M66" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="N66" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O66" t="n">
         <v>2</v>
@@ -3842,10 +3842,10 @@
         <v>1.106898999772966</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1599999964237213</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3854,13 +3854,13 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="N67" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="O67" t="n">
         <v>2</v>
@@ -3893,10 +3893,10 @@
         <v>0.025717673823237</v>
       </c>
       <c r="H68" t="n">
-        <v>1.450000047683716</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I68" t="n">
-        <v>0.05000000074505806</v>
+        <v>0.05999999865889549</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="M68" t="n">
         <v>0.03</v>
       </c>
       <c r="N68" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0.302333887666464</v>
       </c>
       <c r="H69" t="n">
-        <v>2.150000095367432</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2599999904632568</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3956,13 +3956,13 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -3995,10 +3995,10 @@
         <v>1.141721876338126</v>
       </c>
       <c r="H70" t="n">
-        <v>1.25</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I70" t="n">
-        <v>0.9800000190734863</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="M70" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N70" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="O70" t="n">
         <v>2</v>
@@ -4046,10 +4046,10 @@
         <v>0.683145554736262</v>
       </c>
       <c r="H71" t="n">
-        <v>1.080000042915344</v>
+        <v>1.090000033378601</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8700000047683716</v>
+        <v>1.009999990463257</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>0.01</v>
       </c>
       <c r="M71" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="N71" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -4097,7 +4097,7 @@
         <v>1.512542538383604</v>
       </c>
       <c r="H72" t="n">
-        <v>1.870000004768372</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I72" t="n">
         <v>0.3300000131130219</v>
@@ -4109,13 +4109,13 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="M72" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N72" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="O72" t="n">
         <v>4</v>
@@ -4151,7 +4151,7 @@
         <v>0.6499999761581421</v>
       </c>
       <c r="I73" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4199,10 +4199,10 @@
         <v>0.379876299761237</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4300000071525574</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4211,13 +4211,13 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="M74" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="N74" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O74" t="n">
         <v>5</v>
@@ -4250,7 +4250,7 @@
         <v>1.905408421570068</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I75" t="n">
         <v>1.179999947547913</v>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M75" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="N75" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O75" t="n">
         <v>4</v>
@@ -4301,10 +4301,10 @@
         <v>1.147488323971626</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I76" t="n">
-        <v>1.870000004768372</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4313,13 +4313,13 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="M76" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="N76" t="n">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
       <c r="O76" t="n">
         <v>2</v>
@@ -4352,10 +4352,10 @@
         <v>2.067510769702496</v>
       </c>
       <c r="H77" t="n">
-        <v>1.789999961853027</v>
+        <v>1.769999980926514</v>
       </c>
       <c r="I77" t="n">
-        <v>1.309999942779541</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="M77" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="N77" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="O77" t="n">
         <v>3</v>
@@ -4403,7 +4403,7 @@
         <v>0.439149633049963</v>
       </c>
       <c r="H78" t="n">
-        <v>1.350000023841858</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I78" t="n">
         <v>0.4099999964237213</v>
@@ -4415,13 +4415,13 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="M78" t="n">
         <v>0.03</v>
       </c>
       <c r="N78" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -4454,10 +4454,10 @@
         <v>1.752562951296572</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="I79" t="n">
-        <v>1.419999957084656</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4466,13 +4466,13 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="M79" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="N79" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
@@ -4505,10 +4505,10 @@
         <v>1.018078027293079</v>
       </c>
       <c r="H80" t="n">
-        <v>2.059999942779541</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I80" t="n">
-        <v>0.75</v>
+        <v>0.7699999809265137</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="M80" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="N80" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
@@ -4556,10 +4556,10 @@
         <v>1.487884851172557</v>
       </c>
       <c r="H81" t="n">
-        <v>1.450000047683716</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4568,13 +4568,13 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
@@ -4607,10 +4607,10 @@
         <v>0.8294987287372341</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3700000047683716</v>
+        <v>0.3300000131130219</v>
       </c>
       <c r="I82" t="n">
-        <v>1.120000004768372</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="M82" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="N82" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -4658,7 +4658,7 @@
         <v>0.399583207443357</v>
       </c>
       <c r="H83" t="n">
-        <v>1.860000014305115</v>
+        <v>1.75</v>
       </c>
       <c r="I83" t="n">
         <v>0.5400000214576721</v>
@@ -4670,13 +4670,13 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="M83" t="n">
         <v>0.14</v>
       </c>
       <c r="N83" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
@@ -4709,10 +4709,10 @@
         <v>1.125738930888482</v>
       </c>
       <c r="H84" t="n">
-        <v>1.080000042915344</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="M84" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="N84" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="O84" t="n">
         <v>3</v>
@@ -4760,10 +4760,10 @@
         <v>1.593430927954614</v>
       </c>
       <c r="H85" t="n">
-        <v>1.370000004768372</v>
+        <v>1.350000023841858</v>
       </c>
       <c r="I85" t="n">
-        <v>1.379999995231628</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="M85" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="N85" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="O85" t="n">
         <v>4</v>
@@ -4811,10 +4811,10 @@
         <v>0.534137243404987</v>
       </c>
       <c r="H86" t="n">
-        <v>2.089999914169312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I86" t="n">
-        <v>0.7599999904632568</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>1.07</v>
       </c>
       <c r="M86" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="N86" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O86" t="n">
         <v>4</v>
@@ -4862,7 +4862,7 @@
         <v>0.544491930864757</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5600000023841858</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="I87" t="n">
         <v>0.6499999761581421</v>
@@ -4874,13 +4874,13 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="M87" t="n">
         <v>0.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
         <v>1.310101776383825</v>
       </c>
       <c r="H88" t="n">
-        <v>1.649999976158142</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="I88" t="n">
         <v>1.269999980926514</v>
@@ -4925,13 +4925,13 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="M88" t="n">
         <v>0.04</v>
       </c>
       <c r="N88" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="O88" t="n">
         <v>2</v>
@@ -4964,10 +4964,10 @@
         <v>0.692326349206269</v>
       </c>
       <c r="H89" t="n">
-        <v>2.259999990463257</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I89" t="n">
-        <v>1.059999942779541</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -4976,13 +4976,13 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="M89" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="N89" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="O89" t="n">
         <v>3</v>
@@ -5015,10 +5015,10 @@
         <v>0.56493352819234</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5799999833106995</v>
+        <v>0.5899999737739563</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7599999904632568</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5027,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="M90" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="N90" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
@@ -5066,10 +5066,10 @@
         <v>0.4832396986894287</v>
       </c>
       <c r="H91" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="I91" t="n">
-        <v>0.75</v>
+        <v>0.7900000214576721</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -5078,13 +5078,13 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="M91" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="N91" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>0.3749023042619181</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6100000143051147</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5129,10 +5129,10 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="M92" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="N92" t="n">
         <v>0.22</v>
@@ -5168,7 +5168,7 @@
         <v>1.247039115622642</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7400000095367432</v>
+        <v>0.7699999809265137</v>
       </c>
       <c r="I93" t="n">
         <v>0.5</v>
@@ -5180,13 +5180,13 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M93" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N93" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>1.957517564296715</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5899999737739563</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="I94" t="n">
-        <v>1.759999990463257</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5231,13 +5231,13 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M94" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N94" t="n">
         <v>0.2</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0.26</v>
       </c>
       <c r="O94" t="n">
         <v>3</v>
@@ -5270,10 +5270,10 @@
         <v>1.108669703826313</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I95" t="n">
-        <v>1.309999942779541</v>
+        <v>1.259999990463257</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5282,13 +5282,13 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M95" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="N95" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="O95" t="n">
         <v>3</v>
@@ -5321,10 +5321,10 @@
         <v>1.18466504942626</v>
       </c>
       <c r="H96" t="n">
-        <v>1.299999952316284</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.7099999785423279</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5333,13 +5333,13 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M96" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="N96" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -5372,10 +5372,10 @@
         <v>1.515644654670362</v>
       </c>
       <c r="H97" t="n">
-        <v>1.620000004768372</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I97" t="n">
-        <v>1.009999990463257</v>
+        <v>1.029999971389771</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -5384,13 +5384,13 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="M97" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="N97" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -5423,7 +5423,7 @@
         <v>2.958239351399235</v>
       </c>
       <c r="H98" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5</v>
       </c>
       <c r="I98" t="n">
         <v>2.75</v>
@@ -5435,13 +5435,13 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M98" t="n">
         <v>0.21</v>
       </c>
       <c r="N98" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
@@ -5489,7 +5489,7 @@
         <v>0.86</v>
       </c>
       <c r="M99" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="N99" t="n">
         <v>1.24</v>
@@ -5525,10 +5525,10 @@
         <v>1.759099093265829</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9800000190734863</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I100" t="n">
-        <v>1.490000009536743</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M100" t="n">
         <v>0.17</v>
       </c>
-      <c r="M100" t="n">
-        <v>0.27</v>
-      </c>
       <c r="N100" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O100" t="n">
         <v>3</v>
@@ -5576,10 +5576,10 @@
         <v>1.511514868587253</v>
       </c>
       <c r="H101" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="I101" t="n">
-        <v>1.659999966621399</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M101" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="N101" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -5627,10 +5627,10 @@
         <v>0.9744995357468851</v>
       </c>
       <c r="H102" t="n">
-        <v>1.139999985694885</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="I102" t="n">
-        <v>1.190000057220459</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -5642,10 +5642,10 @@
         <v>0.22</v>
       </c>
       <c r="M102" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="N102" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -5678,10 +5678,10 @@
         <v>0.6382359489798539</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9900000095367432</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.4099999964237213</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -5690,13 +5690,13 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="M103" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="N103" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -5729,7 +5729,7 @@
         <v>0.621599402278657</v>
       </c>
       <c r="H104" t="n">
-        <v>0.7400000095367432</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="I104" t="n">
         <v>0.550000011920929</v>
@@ -5741,13 +5741,13 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M104" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N104" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -5780,10 +5780,10 @@
         <v>0.746077122166755</v>
       </c>
       <c r="H105" t="n">
-        <v>1.509999990463257</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I105" t="n">
-        <v>1.009999990463257</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M105" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="N105" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>2.065395319873095</v>
       </c>
       <c r="H106" t="n">
-        <v>1.470000028610229</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0.42</v>
       </c>
       <c r="M106" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="N106" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O106" t="n">
         <v>4</v>
@@ -5882,10 +5882,10 @@
         <v>2.024715404996282</v>
       </c>
       <c r="H107" t="n">
-        <v>1.340000033378601</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -5894,13 +5894,13 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="M107" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="N107" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O107" t="n">
         <v>3</v>
@@ -5984,7 +5984,7 @@
         <v>1.651833647900813</v>
       </c>
       <c r="H109" t="n">
-        <v>1.009999990463257</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I109" t="n">
         <v>0.5699999928474426</v>
@@ -5996,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="M109" t="n">
         <v>1.08</v>
       </c>
       <c r="N109" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O109" t="n">
         <v>4</v>
@@ -6035,10 +6035,10 @@
         <v>1.057036051061005</v>
       </c>
       <c r="H110" t="n">
-        <v>1.230000019073486</v>
+        <v>1.25</v>
       </c>
       <c r="I110" t="n">
-        <v>1.090000033378601</v>
+        <v>1.029999971389771</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="M110" t="n">
         <v>0.03</v>
       </c>
       <c r="N110" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O110" t="n">
         <v>2</v>
@@ -6086,28 +6086,28 @@
         <v>0.6349197630770478</v>
       </c>
       <c r="H111" t="n">
-        <v>1.629999995231628</v>
+        <v>1.799999952316284</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="M111" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N111" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6137,10 +6137,10 @@
         <v>1.425832841545346</v>
       </c>
       <c r="H112" t="n">
-        <v>1.090000033378601</v>
+        <v>1.029999971389771</v>
       </c>
       <c r="I112" t="n">
-        <v>1.090000033378601</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -6149,13 +6149,13 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="M112" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="N112" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="O112" t="n">
         <v>6</v>
@@ -6188,10 +6188,10 @@
         <v>2.335232846477626</v>
       </c>
       <c r="H113" t="n">
-        <v>1.429999947547913</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I113" t="n">
-        <v>1.309999942779541</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -6200,13 +6200,13 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="M113" t="n">
         <v>1.03</v>
       </c>
       <c r="N113" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="O113" t="n">
         <v>3</v>
@@ -6239,10 +6239,10 @@
         <v>1.504167007282386</v>
       </c>
       <c r="H114" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="I114" t="n">
-        <v>1.610000014305115</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -6254,10 +6254,10 @@
         <v>0.31</v>
       </c>
       <c r="M114" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="N114" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="O114" t="n">
         <v>2</v>
@@ -6290,10 +6290,10 @@
         <v>0.7812774647027299</v>
       </c>
       <c r="H115" t="n">
-        <v>1.529999971389771</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="I115" t="n">
-        <v>1.080000042915344</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -6302,13 +6302,13 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="N115" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="O115" t="n">
         <v>4</v>
@@ -6341,10 +6341,10 @@
         <v>1.523827204480769</v>
       </c>
       <c r="H116" t="n">
-        <v>0.800000011920929</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="I116" t="n">
-        <v>1.409999966621399</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -6353,13 +6353,13 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M116" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="N116" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="O116" t="n">
         <v>3</v>
@@ -6392,10 +6392,10 @@
         <v>1.899504314176742</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="I117" t="n">
-        <v>1.320000052452087</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -6404,13 +6404,13 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="M117" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="N117" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="O117" t="n">
         <v>4</v>
@@ -6443,7 +6443,7 @@
         <v>0.4246877189725691</v>
       </c>
       <c r="H118" t="n">
-        <v>1.889999985694885</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="I118" t="n">
         <v>0.3799999952316284</v>
@@ -6455,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="M118" t="n">
         <v>0.05</v>
       </c>
       <c r="N118" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="O118" t="n">
         <v>2</v>
@@ -6494,10 +6494,10 @@
         <v>1.063483301550145</v>
       </c>
       <c r="H119" t="n">
-        <v>1.460000038146973</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6399999856948853</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -6506,13 +6506,13 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="M119" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="N119" t="n">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
@@ -6545,10 +6545,10 @@
         <v>2.806447237730022</v>
       </c>
       <c r="H120" t="n">
-        <v>0.8399999737739563</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="I120" t="n">
-        <v>2.029999971389771</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -6557,13 +6557,13 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="M120" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="N120" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="O120" t="n">
         <v>6</v>
@@ -6596,10 +6596,10 @@
         <v>1.544122571164375</v>
       </c>
       <c r="H121" t="n">
-        <v>2.119999885559082</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="M121" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="N121" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="O121" t="n">
         <v>4</v>
@@ -6647,10 +6647,10 @@
         <v>1.113635398447515</v>
       </c>
       <c r="H122" t="n">
-        <v>1.460000038146973</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0.36</v>
       </c>
       <c r="M122" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="N122" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O122" t="n">
         <v>2</v>
@@ -6698,28 +6698,28 @@
         <v>2.299178114160886</v>
       </c>
       <c r="H123" t="n">
-        <v>1.700000047683716</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="I123" t="n">
-        <v>2.759999990463257</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M123" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="N123" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -6749,10 +6749,10 @@
         <v>1.589235492089392</v>
       </c>
       <c r="H124" t="n">
-        <v>1.039999961853027</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7599999904632568</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -6761,13 +6761,13 @@
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="M124" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="N124" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="O124" t="n">
         <v>2</v>
@@ -6803,7 +6803,7 @@
         <v>1.610000014305115</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5699999928474426</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -6812,13 +6812,13 @@
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M125" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="N125" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="O125" t="n">
         <v>3</v>
@@ -6851,10 +6851,10 @@
         <v>0.738628979772334</v>
       </c>
       <c r="H126" t="n">
-        <v>1.5</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I126" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M126" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="N126" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -6902,10 +6902,10 @@
         <v>1.744463023768363</v>
       </c>
       <c r="H127" t="n">
-        <v>0.7300000190734863</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9700000286102295</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -6914,13 +6914,13 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="M127" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="N127" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="O127" t="n">
         <v>3</v>
@@ -6953,28 +6953,28 @@
         <v>2.004293492995193</v>
       </c>
       <c r="H128" t="n">
-        <v>1.509999990463257</v>
+        <v>1.220000028610229</v>
       </c>
       <c r="I128" t="n">
-        <v>1.830000042915344</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="M128" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="N128" t="n">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -7004,10 +7004,10 @@
         <v>1.599439857527619</v>
       </c>
       <c r="H129" t="n">
-        <v>2.049999952316284</v>
+        <v>2.009999990463257</v>
       </c>
       <c r="I129" t="n">
-        <v>1.820000052452087</v>
+        <v>1.799999952316284</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -7016,13 +7016,13 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="M129" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="N129" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="O129" t="n">
         <v>2</v>
@@ -7055,10 +7055,10 @@
         <v>1.173688435927034</v>
       </c>
       <c r="H130" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I130" t="n">
-        <v>1.090000033378601</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -7067,13 +7067,13 @@
         <v>1</v>
       </c>
       <c r="L130" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M130" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="N130" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -7106,10 +7106,10 @@
         <v>2.133399207144965</v>
       </c>
       <c r="H131" t="n">
-        <v>2.539999961853027</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="I131" t="n">
-        <v>1.419999957084656</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -7118,13 +7118,13 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="M131" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="N131" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
         <v>4</v>
@@ -7157,10 +7157,10 @@
         <v>1.228155044877531</v>
       </c>
       <c r="H132" t="n">
-        <v>1.25</v>
+        <v>1.309999942779541</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5899999737739563</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -7169,13 +7169,13 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M132" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N132" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="O132" t="n">
         <v>4</v>
@@ -7208,10 +7208,10 @@
         <v>1.024829615838827</v>
       </c>
       <c r="H133" t="n">
-        <v>1.620000004768372</v>
+        <v>1.649999976158142</v>
       </c>
       <c r="I133" t="n">
-        <v>1.320000052452087</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -7220,13 +7220,13 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="M133" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="N133" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="O133" t="n">
         <v>4</v>
@@ -7259,10 +7259,10 @@
         <v>1.58029273063093</v>
       </c>
       <c r="H134" t="n">
-        <v>1.25</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I134" t="n">
-        <v>0.949999988079071</v>
+        <v>1.009999990463257</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -7271,13 +7271,13 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="M134" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="N134" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O134" t="n">
         <v>4</v>
@@ -7310,10 +7310,10 @@
         <v>0.9137102840468209</v>
       </c>
       <c r="H135" t="n">
-        <v>1.179999947547913</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I135" t="n">
-        <v>1.080000042915344</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="M135" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="N135" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="O135" t="n">
         <v>2</v>
@@ -7364,7 +7364,7 @@
         <v>1.220000028610229</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6000000238418579</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -7376,10 +7376,10 @@
         <v>0.6</v>
       </c>
       <c r="M136" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="N136" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -7412,10 +7412,10 @@
         <v>1.148553748615075</v>
       </c>
       <c r="H137" t="n">
-        <v>1.360000014305115</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="I137" t="n">
-        <v>1.549999952316284</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -7424,13 +7424,13 @@
         <v>1</v>
       </c>
       <c r="L137" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="M137" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N137" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="O137" t="n">
         <v>1</v>
@@ -7463,10 +7463,10 @@
         <v>0.288695776835085</v>
       </c>
       <c r="H138" t="n">
-        <v>1.259999990463257</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3899999856948853</v>
+        <v>0.3700000047683716</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -7475,13 +7475,13 @@
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="M138" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="N138" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O138" t="n">
         <v>3</v>
@@ -7514,10 +7514,10 @@
         <v>1.238630831280357</v>
       </c>
       <c r="H139" t="n">
-        <v>1.799999952316284</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="I139" t="n">
-        <v>0.449999988079071</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -7526,13 +7526,13 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="M139" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="N139" t="n">
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="O139" t="n">
         <v>1</v>
@@ -7565,10 +7565,10 @@
         <v>1.597315314264593</v>
       </c>
       <c r="H140" t="n">
-        <v>1.480000019073486</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7599999904632568</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="M140" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="N140" t="n">
         <v>1.15</v>
@@ -7616,10 +7616,10 @@
         <v>1.695289418101309</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="I141" t="n">
-        <v>1.970000028610229</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -7628,13 +7628,13 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="M141" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="N141" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="O141" t="n">
         <v>5</v>
@@ -7667,7 +7667,7 @@
         <v>0.260138837620616</v>
       </c>
       <c r="H142" t="n">
-        <v>2.299999952316284</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I142" t="n">
         <v>0.3600000143051147</v>
@@ -7679,13 +7679,13 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="M142" t="n">
         <v>0.1</v>
       </c>
       <c r="N142" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O142" t="n">
         <v>1</v>
@@ -7718,10 +7718,10 @@
         <v>0.6853457116521897</v>
       </c>
       <c r="H143" t="n">
-        <v>1.570000052452087</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -7733,10 +7733,10 @@
         <v>0.53</v>
       </c>
       <c r="M143" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="N143" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -7769,10 +7769,10 @@
         <v>1.382870627567173</v>
       </c>
       <c r="H144" t="n">
-        <v>1.730000019073486</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I144" t="n">
-        <v>1.639999985694885</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -7781,10 +7781,10 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M144" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="N144" t="n">
         <v>0.91</v>
@@ -7820,10 +7820,10 @@
         <v>0.7564517669379721</v>
       </c>
       <c r="H145" t="n">
-        <v>2.319999933242798</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6200000047683716</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -7832,13 +7832,13 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="M145" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="N145" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="O145" t="n">
         <v>3</v>
@@ -7871,10 +7871,10 @@
         <v>1.045819129794839</v>
       </c>
       <c r="H146" t="n">
-        <v>1.279999971389771</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="I146" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -7883,13 +7883,13 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="M146" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="N146" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="O146" t="n">
         <v>4</v>
@@ -7925,7 +7925,7 @@
         <v>1.879999995231628</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -7940,7 +7940,7 @@
         <v>0.02</v>
       </c>
       <c r="N147" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="O147" t="n">
         <v>3</v>
@@ -7973,10 +7973,10 @@
         <v>1.282259892672299</v>
       </c>
       <c r="H148" t="n">
-        <v>1.320000052452087</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="M148" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="N148" t="n">
         <v>0.37</v>
@@ -8024,10 +8024,10 @@
         <v>1.269886596128349</v>
       </c>
       <c r="H149" t="n">
-        <v>0.3600000143051147</v>
+        <v>0.3799999952316284</v>
       </c>
       <c r="I149" t="n">
-        <v>1.600000023841858</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -8036,13 +8036,13 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="M149" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="N149" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="O149" t="n">
         <v>3</v>
@@ -8075,10 +8075,10 @@
         <v>1.684195360168813</v>
       </c>
       <c r="H150" t="n">
-        <v>1.129999995231628</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -8087,13 +8087,13 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="M150" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="N150" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="O150" t="n">
         <v>1</v>
@@ -8126,10 +8126,10 @@
         <v>0.5511507056653513</v>
       </c>
       <c r="H151" t="n">
-        <v>1.399999976158142</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="I151" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -8138,13 +8138,13 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="M151" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="N151" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="O151" t="n">
         <v>1</v>
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M152" t="n">
         <v>0.11</v>
@@ -8228,10 +8228,10 @@
         <v>1.454973110929129</v>
       </c>
       <c r="H153" t="n">
-        <v>1.740000009536743</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="I153" t="n">
-        <v>1.519999980926514</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -8240,13 +8240,13 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="M153" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="N153" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="O153" t="n">
         <v>3</v>
@@ -8279,10 +8279,10 @@
         <v>2.537615714633459</v>
       </c>
       <c r="H154" t="n">
-        <v>1.379999995231628</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I154" t="n">
-        <v>1.509999990463257</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -8291,13 +8291,13 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="M154" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="N154" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="O154" t="n">
         <v>4</v>
@@ -8330,10 +8330,10 @@
         <v>1.714497945310171</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="I155" t="n">
-        <v>0.7400000095367432</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -8342,13 +8342,13 @@
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="M155" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="N155" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
@@ -8381,10 +8381,10 @@
         <v>0.6427058503031789</v>
       </c>
       <c r="H156" t="n">
-        <v>2.579999923706055</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I156" t="n">
-        <v>0.6000000238418579</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -8393,13 +8393,13 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="M156" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="N156" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="O156" t="n">
         <v>6</v>
@@ -8432,10 +8432,10 @@
         <v>1.441101446747793</v>
       </c>
       <c r="H157" t="n">
-        <v>0.6000000238418579</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="I157" t="n">
-        <v>2.039999961853027</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -8444,10 +8444,10 @@
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="N157" t="n">
         <v>0.8</v>
@@ -8483,10 +8483,10 @@
         <v>0.248423960059882</v>
       </c>
       <c r="H158" t="n">
-        <v>1.740000009536743</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3199999928474426</v>
+        <v>0.300000011920929</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -8495,13 +8495,13 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="M158" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N158" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -8534,10 +8534,10 @@
         <v>0.491910379379987</v>
       </c>
       <c r="H159" t="n">
-        <v>2.039999961853027</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6499999761581421</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="M159" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="N159" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="O159" t="n">
         <v>1</v>
@@ -8585,10 +8585,10 @@
         <v>0.7949470169842229</v>
       </c>
       <c r="H160" t="n">
-        <v>1.320000052452087</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -8597,13 +8597,13 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="M160" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="N160" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="O160" t="n">
         <v>5</v>
@@ -8636,10 +8636,10 @@
         <v>1.265282576942443</v>
       </c>
       <c r="H161" t="n">
-        <v>1.700000047683716</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I161" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -8648,13 +8648,13 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="M161" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N161" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O161" t="n">
         <v>4</v>
@@ -8687,10 +8687,10 @@
         <v>1.231319722719495</v>
       </c>
       <c r="H162" t="n">
-        <v>1.100000023841858</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="I162" t="n">
-        <v>1.809999942779541</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -8699,13 +8699,13 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="M162" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="N162" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -8738,10 +8738,10 @@
         <v>1.458083111792801</v>
       </c>
       <c r="H163" t="n">
-        <v>0.6499999761581421</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I163" t="n">
-        <v>2.019999980926514</v>
+        <v>1.940000057220459</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -8750,13 +8750,13 @@
         <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="M163" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="N163" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="O163" t="n">
         <v>2</v>
@@ -8789,10 +8789,10 @@
         <v>0.929207556881015</v>
       </c>
       <c r="H164" t="n">
-        <v>1.730000019073486</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6000000238418579</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -8801,13 +8801,13 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="N164" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="O164" t="n">
         <v>3</v>
@@ -8840,10 +8840,10 @@
         <v>0.550594668835403</v>
       </c>
       <c r="H165" t="n">
-        <v>1.029999971389771</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I165" t="n">
-        <v>1.129999995231628</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -8852,13 +8852,13 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="M165" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="N165" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="O165" t="n">
         <v>2</v>
@@ -8891,7 +8891,7 @@
         <v>1.737389195710424</v>
       </c>
       <c r="H166" t="n">
-        <v>0.4300000071525574</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="I166" t="n">
         <v>2.269999980926514</v>
@@ -8903,13 +8903,13 @@
         <v>1</v>
       </c>
       <c r="L166" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="M166" t="n">
         <v>0.53</v>
       </c>
       <c r="N166" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="n">
         <v>1</v>
@@ -8942,7 +8942,7 @@
         <v>0.393704540096223</v>
       </c>
       <c r="H167" t="n">
-        <v>1.330000042915344</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I167" t="n">
         <v>0.4900000095367432</v>
@@ -8954,13 +8954,13 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="M167" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N167" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="O167" t="n">
         <v>2</v>
@@ -8993,10 +8993,10 @@
         <v>2.568035963922731</v>
       </c>
       <c r="H168" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I168" t="n">
-        <v>2.490000009536743</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -9005,13 +9005,13 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="M168" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="N168" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="O168" t="n">
         <v>2</v>
@@ -9044,10 +9044,10 @@
         <v>1.626160908490413</v>
       </c>
       <c r="H169" t="n">
-        <v>1.039999961853027</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>1.049999952316284</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -9056,13 +9056,13 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="M169" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="N169" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="O169" t="n">
         <v>2</v>
@@ -9095,10 +9095,10 @@
         <v>1.154966605827213</v>
       </c>
       <c r="H170" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="I170" t="n">
-        <v>1.25</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -9107,13 +9107,13 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M170" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="O170" t="n">
         <v>1</v>
@@ -9146,10 +9146,10 @@
         <v>0.697622751817102</v>
       </c>
       <c r="H171" t="n">
-        <v>1.690000057220459</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I171" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -9158,13 +9158,13 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="M171" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="N171" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="O171" t="n">
         <v>4</v>
@@ -9197,10 +9197,10 @@
         <v>0.701498975977302</v>
       </c>
       <c r="H172" t="n">
-        <v>0.5</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -9209,13 +9209,13 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M172" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N172" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -9248,10 +9248,10 @@
         <v>0.590074462816124</v>
       </c>
       <c r="H173" t="n">
-        <v>1.340000033378601</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2300000041723251</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -9260,13 +9260,13 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="M173" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="N173" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="O173" t="n">
         <v>1</v>
@@ -9299,10 +9299,10 @@
         <v>0.5648306794464569</v>
       </c>
       <c r="H174" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="I174" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -9311,10 +9311,10 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="M174" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="N174" t="n">
         <v>0.5600000000000001</v>
@@ -9350,7 +9350,7 @@
         <v>1.204920929390931</v>
       </c>
       <c r="H175" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.9900000095367432</v>
       </c>
       <c r="I175" t="n">
         <v>1.240000009536743</v>
@@ -9362,13 +9362,13 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="M175" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N175" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="O175" t="n">
         <v>2</v>
@@ -9401,7 +9401,7 @@
         <v>0.284416534006598</v>
       </c>
       <c r="H176" t="n">
-        <v>2.369999885559082</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="I176" t="n">
         <v>0.2599999904632568</v>
@@ -9413,13 +9413,13 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="M176" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N176" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="O176" t="n">
         <v>2</v>
@@ -9452,10 +9452,10 @@
         <v>0.796033139340575</v>
       </c>
       <c r="H177" t="n">
-        <v>1.990000009536743</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9700000286102295</v>
+        <v>0.9900000095367432</v>
       </c>
       <c r="J177" t="n">
         <v>1</v>
@@ -9464,13 +9464,13 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="M177" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N177" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>1.858760166913275</v>
       </c>
       <c r="H178" t="n">
-        <v>0.5600000023841858</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="I178" t="n">
-        <v>1.570000052452087</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -9515,13 +9515,13 @@
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="M178" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="N178" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="O178" t="n">
         <v>2</v>
@@ -9554,10 +9554,10 @@
         <v>0.7310228534042799</v>
       </c>
       <c r="H179" t="n">
-        <v>2.789999961853027</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6000000238418579</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="J179" t="n">
         <v>1</v>
@@ -9566,13 +9566,13 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="M179" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="N179" t="n">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -9605,10 +9605,10 @@
         <v>1.547060360200699</v>
       </c>
       <c r="H180" t="n">
-        <v>0.2800000011920929</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="I180" t="n">
-        <v>1.769999980926514</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -9617,13 +9617,13 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="M180" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="N180" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="O180" t="n">
         <v>3</v>
@@ -9656,10 +9656,10 @@
         <v>0.9661311190575327</v>
       </c>
       <c r="H181" t="n">
-        <v>2.619999885559082</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I181" t="n">
-        <v>0.75</v>
+        <v>0.7900000214576721</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -9668,13 +9668,13 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="M181" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="N181" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O181" t="n">
         <v>4</v>
@@ -9707,10 +9707,10 @@
         <v>1.670245617666837</v>
       </c>
       <c r="H182" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.699999988079071</v>
       </c>
       <c r="I182" t="n">
-        <v>1.159999966621399</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -9719,13 +9719,13 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="M182" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="N182" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="O182" t="n">
         <v>3</v>
@@ -9758,10 +9758,10 @@
         <v>1.330370888113979</v>
       </c>
       <c r="H183" t="n">
-        <v>0.3899999856948853</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="I183" t="n">
-        <v>1.139999985694885</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -9770,13 +9770,13 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M183" t="n">
         <v>0.16</v>
       </c>
-      <c r="M183" t="n">
-        <v>0.19</v>
-      </c>
       <c r="N183" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="O183" t="n">
         <v>2</v>
@@ -9809,10 +9809,10 @@
         <v>2.574069147929543</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2599999904632568</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="I184" t="n">
-        <v>1.879999995231628</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -9821,13 +9821,13 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M184" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="N184" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="O184" t="n">
         <v>3</v>
@@ -9860,10 +9860,10 @@
         <v>1.383701642975217</v>
       </c>
       <c r="H185" t="n">
-        <v>1.360000014305115</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I185" t="n">
-        <v>1.019999980926514</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -9872,13 +9872,13 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="M185" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="N185" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="O185" t="n">
         <v>2</v>
@@ -9911,10 +9911,10 @@
         <v>1.803652124518158</v>
       </c>
       <c r="H186" t="n">
-        <v>1.5</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I186" t="n">
-        <v>1.019999980926514</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -9923,13 +9923,13 @@
         <v>1</v>
       </c>
       <c r="L186" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="M186" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="N186" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="O186" t="n">
         <v>3</v>
@@ -9962,10 +9962,10 @@
         <v>1.719655482137201</v>
       </c>
       <c r="H187" t="n">
-        <v>1.549999952316284</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -9974,13 +9974,13 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M187" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="N187" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O187" t="n">
         <v>4</v>
@@ -10013,10 +10013,10 @@
         <v>2.574432352557778</v>
       </c>
       <c r="H188" t="n">
-        <v>0.3600000143051147</v>
+        <v>0.3300000131130219</v>
       </c>
       <c r="I188" t="n">
-        <v>2.720000028610229</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -10025,13 +10025,13 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="N188" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="O188" t="n">
         <v>2</v>
@@ -10064,10 +10064,10 @@
         <v>2.15103163570165</v>
       </c>
       <c r="H189" t="n">
-        <v>1.460000038146973</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="I189" t="n">
-        <v>1.549999952316284</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -10076,13 +10076,13 @@
         <v>1</v>
       </c>
       <c r="L189" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="M189" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N189" t="n">
         <v>0.6</v>
-      </c>
-      <c r="N189" t="n">
-        <v>0.97</v>
       </c>
       <c r="O189" t="n">
         <v>2</v>
@@ -10115,10 +10115,10 @@
         <v>1.797852410003529</v>
       </c>
       <c r="H190" t="n">
-        <v>1.309999942779541</v>
+        <v>1.200000047683716</v>
       </c>
       <c r="I190" t="n">
-        <v>2.130000114440918</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -10127,13 +10127,13 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="M190" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="N190" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="O190" t="n">
         <v>4</v>
@@ -10166,10 +10166,10 @@
         <v>1.320813206063208</v>
       </c>
       <c r="H191" t="n">
-        <v>3.259999990463257</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="I191" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5600000023841858</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -10178,13 +10178,13 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="M191" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="N191" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="O191" t="n">
         <v>2</v>
@@ -10217,10 +10217,10 @@
         <v>1.219854926690454</v>
       </c>
       <c r="H192" t="n">
-        <v>1.200000047683716</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="I192" t="n">
-        <v>1.200000047683716</v>
+        <v>1.25</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -10229,13 +10229,13 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="M192" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N192" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="O192" t="n">
         <v>2</v>
@@ -10268,10 +10268,10 @@
         <v>1.795822645537553</v>
       </c>
       <c r="H193" t="n">
-        <v>1.210000038146973</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I193" t="n">
-        <v>1.620000004768372</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -10280,13 +10280,13 @@
         <v>1</v>
       </c>
       <c r="L193" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="M193" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="N193" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="O193" t="n">
         <v>3</v>
@@ -10322,7 +10322,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -10334,10 +10334,10 @@
         <v>0.15</v>
       </c>
       <c r="M194" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="N194" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="O194" t="n">
         <v>2</v>
@@ -10370,10 +10370,10 @@
         <v>0.815921616740531</v>
       </c>
       <c r="H195" t="n">
-        <v>1.700000047683716</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="I195" t="n">
-        <v>1.100000023841858</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -10382,13 +10382,13 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="M195" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="N195" t="n">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="O195" t="n">
         <v>2</v>
@@ -10421,10 +10421,10 @@
         <v>1.040125666186217</v>
       </c>
       <c r="H196" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I196" t="n">
-        <v>1.159999966621399</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -10433,13 +10433,13 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M196" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="N196" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="O196" t="n">
         <v>3</v>
@@ -10472,10 +10472,10 @@
         <v>1.511428046971558</v>
       </c>
       <c r="H197" t="n">
-        <v>2.170000076293945</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="I197" t="n">
-        <v>1.259999990463257</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -10484,13 +10484,13 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="M197" t="n">
         <v>0.25</v>
       </c>
       <c r="N197" t="n">
-        <v>0.52</v>
+        <v>0.29</v>
       </c>
       <c r="O197" t="n">
         <v>2</v>
@@ -10526,7 +10526,7 @@
         <v>0.6299999952316284</v>
       </c>
       <c r="I198" t="n">
-        <v>1.610000014305115</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -10538,10 +10538,10 @@
         <v>0.1</v>
       </c>
       <c r="M198" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="N198" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="O198" t="n">
         <v>1</v>
@@ -10574,7 +10574,7 @@
         <v>0.711492316797373</v>
       </c>
       <c r="H199" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I199" t="n">
         <v>0.9800000190734863</v>
@@ -10586,13 +10586,13 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="M199" t="n">
         <v>0.27</v>
       </c>
       <c r="N199" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O199" t="n">
         <v>4</v>
@@ -10625,10 +10625,10 @@
         <v>1.26268549077212</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7300000190734863</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="I200" t="n">
-        <v>1.070000052452087</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -10637,13 +10637,13 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M200" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="N200" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="O200" t="n">
         <v>3</v>
@@ -10676,10 +10676,10 @@
         <v>0.9358670730143841</v>
       </c>
       <c r="H201" t="n">
-        <v>1.720000028610229</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="I201" t="n">
-        <v>1.139999985694885</v>
+        <v>1.080000042915344</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -10688,13 +10688,13 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N201" t="n">
         <v>2.37</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N201" t="n">
-        <v>2.57</v>
       </c>
       <c r="O201" t="n">
         <v>5</v>
@@ -10727,28 +10727,28 @@
         <v>1.149427298456429</v>
       </c>
       <c r="H202" t="n">
-        <v>1.360000014305115</v>
+        <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>1.669999957084656</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="M202" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="N202" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="O202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -10781,7 +10781,7 @@
         <v>0.2700000107288361</v>
       </c>
       <c r="I203" t="n">
-        <v>1.649999976158142</v>
+        <v>1.610000014305115</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0.05</v>
       </c>
       <c r="M203" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N203" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O203" t="n">
         <v>1</v>
@@ -10829,10 +10829,10 @@
         <v>0.9085050383582675</v>
       </c>
       <c r="H204" t="n">
-        <v>0.7200000286102295</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="I204" t="n">
-        <v>1.220000028610229</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="M204" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="N204" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="O204" t="n">
         <v>1</v>
@@ -10880,10 +10880,10 @@
         <v>1.346712451893841</v>
       </c>
       <c r="H205" t="n">
-        <v>0.25</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="I205" t="n">
-        <v>1.629999995231628</v>
+        <v>1.75</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -10892,13 +10892,13 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="M205" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="N205" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="O205" t="n">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="I206" t="n">
-        <v>1.269999980926514</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -10943,13 +10943,13 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="M206" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="N206" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -10982,10 +10982,10 @@
         <v>1.363441899418838</v>
       </c>
       <c r="H207" t="n">
-        <v>1.629999995231628</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="I207" t="n">
-        <v>1.649999976158142</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -10994,13 +10994,13 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M207" t="n">
-        <v>0.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N207" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="O207" t="n">
         <v>3</v>
@@ -11033,10 +11033,10 @@
         <v>1.859705833718173</v>
       </c>
       <c r="H208" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="I208" t="n">
-        <v>1.480000019073486</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -11045,13 +11045,13 @@
         <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="M208" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="N208" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="O208" t="n">
         <v>2</v>
@@ -11084,7 +11084,7 @@
         <v>0.167642027139664</v>
       </c>
       <c r="H209" t="n">
-        <v>2.900000095367432</v>
+        <v>3.25</v>
       </c>
       <c r="I209" t="n">
         <v>0.2800000011920929</v>
@@ -11096,13 +11096,13 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="M209" t="n">
         <v>0.11</v>
       </c>
       <c r="N209" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="O209" t="n">
         <v>1</v>
@@ -11135,10 +11135,10 @@
         <v>0.49370351806283</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6399999856948853</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M210" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="N210" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>0.3899999856948853</v>
       </c>
       <c r="I211" t="n">
-        <v>1.259999990463257</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -11237,10 +11237,10 @@
         <v>0.348652336746454</v>
       </c>
       <c r="H212" t="n">
-        <v>5.03000020980835</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3899999856948853</v>
       </c>
       <c r="J212" t="n">
         <v>1</v>
@@ -11249,13 +11249,13 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="M212" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N212" t="n">
         <v>0.05</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0.12</v>
       </c>
       <c r="O212" t="n">
         <v>7</v>
@@ -11288,10 +11288,10 @@
         <v>0.515181334689255</v>
       </c>
       <c r="H213" t="n">
-        <v>1.460000038146973</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -11300,13 +11300,13 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M213" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="N213" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O213" t="n">
         <v>6</v>
@@ -11339,28 +11339,28 @@
         <v>1.281785547733313</v>
       </c>
       <c r="H214" t="n">
-        <v>2.410000085830688</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="J214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="M214" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="N214" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="O214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
@@ -11390,10 +11390,10 @@
         <v>0.368747435510158</v>
       </c>
       <c r="H215" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -11402,13 +11402,13 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M215" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="N215" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -11441,10 +11441,10 @@
         <v>0.658326965756719</v>
       </c>
       <c r="H216" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="I216" t="n">
-        <v>0.6399999856948853</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -11453,13 +11453,13 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="M216" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="O216" t="n">
         <v>1</v>
@@ -11492,10 +11492,10 @@
         <v>1.654719011858103</v>
       </c>
       <c r="H217" t="n">
-        <v>3.509999990463257</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I217" t="n">
-        <v>1.669999957084656</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>3</v>
@@ -11504,13 +11504,13 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="M217" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="N217" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="O217" t="n">
         <v>1</v>
@@ -11543,10 +11543,10 @@
         <v>0.5545936645939985</v>
       </c>
       <c r="H218" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -11555,13 +11555,13 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="M218" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="N218" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="O218" t="n">
         <v>5</v>
@@ -11594,10 +11594,10 @@
         <v>0.525286132469768</v>
       </c>
       <c r="H219" t="n">
-        <v>1.110000014305115</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7099999785423279</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -11606,13 +11606,13 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="M219" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="N219" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="O219" t="n">
         <v>3</v>
@@ -11645,10 +11645,10 @@
         <v>0.4451905945316</v>
       </c>
       <c r="H220" t="n">
-        <v>1.539999961853027</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4099999964237213</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -11657,13 +11657,13 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="M220" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="N220" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="O220" t="n">
         <v>2</v>
@@ -11696,10 +11696,10 @@
         <v>1.685942312702547</v>
       </c>
       <c r="H221" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="I221" t="n">
-        <v>1.480000019073486</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -11708,13 +11708,13 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="M221" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="N221" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="O221" t="n">
         <v>4</v>
@@ -11747,10 +11747,10 @@
         <v>1.755172023588419</v>
       </c>
       <c r="H222" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="I222" t="n">
-        <v>1.330000042915344</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -11759,13 +11759,13 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M222" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="N222" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="O222" t="n">
         <v>5</v>
@@ -11792,16 +11792,16 @@
         <v>3</v>
       </c>
       <c r="F223" t="n">
-        <v>2.127215683460234</v>
+        <v>1.063607841730117</v>
       </c>
       <c r="G223" t="n">
-        <v>4.529724260792147</v>
+        <v>2.264862130396074</v>
       </c>
       <c r="H223" t="n">
-        <v>1.870000004768372</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="I223" t="n">
-        <v>4.699999809265137</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -11810,13 +11810,13 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="M223" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="N223" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O223" t="n">
         <v>4</v>
@@ -11849,10 +11849,10 @@
         <v>1.258103241212657</v>
       </c>
       <c r="H224" t="n">
-        <v>2.460000038146973</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="I224" t="n">
-        <v>1.740000009536743</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="J224" t="n">
         <v>1</v>
@@ -11861,13 +11861,13 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="M224" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="N224" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="O224" t="n">
         <v>2</v>
@@ -11900,10 +11900,10 @@
         <v>0.471465026959771</v>
       </c>
       <c r="H225" t="n">
-        <v>1.610000014305115</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.5899999737739563</v>
       </c>
       <c r="J225" t="n">
         <v>1</v>
@@ -11912,13 +11912,13 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="M225" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="N225" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="O225" t="n">
         <v>3</v>
@@ -11954,7 +11954,7 @@
         <v>1.870000004768372</v>
       </c>
       <c r="I226" t="n">
-        <v>0.7200000286102295</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -11966,10 +11966,10 @@
         <v>0.06</v>
       </c>
       <c r="M226" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="N226" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>0.6664145365357419</v>
       </c>
       <c r="H227" t="n">
-        <v>3.25</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="I227" t="n">
         <v>0.7900000214576721</v>
@@ -12014,13 +12014,13 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M227" t="n">
         <v>0.13</v>
       </c>
       <c r="N227" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O227" t="n">
         <v>1</v>
@@ -12053,10 +12053,10 @@
         <v>1.413724530488247</v>
       </c>
       <c r="H228" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="I228" t="n">
-        <v>1.690000057220459</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -12065,13 +12065,13 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M228" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="N228" t="n">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="O228" t="n">
         <v>2</v>
@@ -12104,10 +12104,10 @@
         <v>4.311818510293958</v>
       </c>
       <c r="H229" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="I229" t="n">
-        <v>3.480000019073486</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -12116,13 +12116,13 @@
         <v>2</v>
       </c>
       <c r="L229" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="M229" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="N229" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="O229" t="n">
         <v>3</v>
@@ -12155,7 +12155,7 @@
         <v>0.7418482247740099</v>
       </c>
       <c r="H230" t="n">
-        <v>0.2700000107288361</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="I230" t="n">
         <v>0.9100000262260437</v>
@@ -12167,13 +12167,13 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="M230" t="n">
         <v>0.17</v>
       </c>
       <c r="N230" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="O230" t="n">
         <v>1</v>
@@ -12206,10 +12206,10 @@
         <v>2.820300994479656</v>
       </c>
       <c r="H231" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="I231" t="n">
-        <v>1.330000042915344</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -12218,13 +12218,13 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="M231" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="N231" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="O231" t="n">
         <v>3</v>
@@ -12260,7 +12260,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0.04</v>
       </c>
       <c r="M232" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="N232" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -12308,7 +12308,7 @@
         <v>2.560501286798734</v>
       </c>
       <c r="H233" t="n">
-        <v>0.8600000143051147</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="I233" t="n">
         <v>1.240000009536743</v>
@@ -12320,13 +12320,13 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="M233" t="n">
         <v>1.32</v>
       </c>
       <c r="N233" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="O233" t="n">
         <v>5</v>
@@ -12359,10 +12359,10 @@
         <v>0.961176044307653</v>
       </c>
       <c r="H234" t="n">
-        <v>2.059999942779541</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>1.090000033378601</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
       <c r="M234" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="N234" t="n">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="O234" t="n">
         <v>4</v>
@@ -12410,7 +12410,7 @@
         <v>0.183589162304998</v>
       </c>
       <c r="H235" t="n">
-        <v>1.620000004768372</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I235" t="n">
         <v>0.1700000017881393</v>
@@ -12422,13 +12422,13 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="M235" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="N235" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="O235" t="n">
         <v>1</v>
@@ -12461,7 +12461,7 @@
         <v>0.8938320260882381</v>
       </c>
       <c r="H236" t="n">
-        <v>1.340000033378601</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="I236" t="n">
         <v>0.2300000041723251</v>
@@ -12473,13 +12473,13 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="M236" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="N236" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="O236" t="n">
         <v>3</v>
@@ -12512,10 +12512,10 @@
         <v>2.569157960824672</v>
       </c>
       <c r="H237" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="I237" t="n">
-        <v>2.410000085830688</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -12524,13 +12524,13 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M237" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N237" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="O237" t="n">
         <v>5</v>
@@ -12563,10 +12563,10 @@
         <v>1.170549040660266</v>
       </c>
       <c r="H238" t="n">
-        <v>3.180000066757202</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9900000095367432</v>
+        <v>0.9399999976158142</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -12575,13 +12575,13 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="M238" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="N238" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="O238" t="n">
         <v>4</v>
@@ -12614,7 +12614,7 @@
         <v>0.986563272774218</v>
       </c>
       <c r="H239" t="n">
-        <v>2.630000114440918</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="I239" t="n">
         <v>0.8700000047683716</v>
@@ -12626,13 +12626,13 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="M239" t="n">
         <v>0.12</v>
       </c>
       <c r="N239" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="O239" t="n">
         <v>3</v>
@@ -12665,10 +12665,10 @@
         <v>0.5081987674348042</v>
       </c>
       <c r="H240" t="n">
-        <v>1.75</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3499999940395355</v>
+        <v>0.3700000047683716</v>
       </c>
       <c r="J240" t="n">
         <v>1</v>
@@ -12677,13 +12677,13 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="M240" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="N240" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="O240" t="n">
         <v>1</v>
@@ -12716,10 +12716,10 @@
         <v>1.333090487867601</v>
       </c>
       <c r="H241" t="n">
-        <v>0.6600000262260437</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="I241" t="n">
-        <v>0.9700000286102295</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -12731,10 +12731,10 @@
         <v>0.1</v>
       </c>
       <c r="M241" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="N241" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="O241" t="n">
         <v>2</v>
@@ -12767,10 +12767,10 @@
         <v>2.329433400222673</v>
       </c>
       <c r="H242" t="n">
-        <v>0.449999988079071</v>
+        <v>0.4099999964237213</v>
       </c>
       <c r="I242" t="n">
-        <v>1.149999976158142</v>
+        <v>1.190000057220459</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -12779,10 +12779,10 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="M242" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="N242" t="n">
         <v>1.5</v>
@@ -12818,10 +12818,10 @@
         <v>1.615593668112159</v>
       </c>
       <c r="H243" t="n">
-        <v>1.269999980926514</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5699999928474426</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -12830,13 +12830,13 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="M243" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N243" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O243" t="n">
         <v>3</v>
@@ -12869,10 +12869,10 @@
         <v>1.59035259628817</v>
       </c>
       <c r="H244" t="n">
-        <v>1.669999957084656</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I244" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.7699999809265137</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -12881,13 +12881,13 @@
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="M244" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="N244" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O244" t="n">
         <v>2</v>
@@ -12920,10 +12920,10 @@
         <v>0.9344942308962321</v>
       </c>
       <c r="H245" t="n">
-        <v>1.860000014305115</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="I245" t="n">
-        <v>1.169999957084656</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -12932,13 +12932,13 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="M245" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="N245" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="O245" t="n">
         <v>5</v>
@@ -12971,10 +12971,10 @@
         <v>1.327519038692118</v>
       </c>
       <c r="H246" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="I246" t="n">
-        <v>1.330000042915344</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -12983,13 +12983,13 @@
         <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="N246" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="O246" t="n">
         <v>2</v>
@@ -13022,10 +13022,10 @@
         <v>1.341924292035418</v>
       </c>
       <c r="H247" t="n">
-        <v>2.720000028610229</v>
+        <v>2.75</v>
       </c>
       <c r="I247" t="n">
-        <v>1.860000014305115</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="J247" t="n">
         <v>1</v>
@@ -13034,13 +13034,13 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="M247" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="N247" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="O247" t="n">
         <v>1</v>
@@ -13073,7 +13073,7 @@
         <v>0.890591293612123</v>
       </c>
       <c r="H248" t="n">
-        <v>1.950000047683716</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="I248" t="n">
         <v>0.1000000014901161</v>
@@ -13085,13 +13085,13 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
       <c r="M248" t="n">
         <v>0.79</v>
       </c>
       <c r="N248" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="O248" t="n">
         <v>3</v>
@@ -13124,10 +13124,10 @@
         <v>2.058509637793895</v>
       </c>
       <c r="H249" t="n">
-        <v>0.449999988079071</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I249" t="n">
-        <v>1.980000019073486</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -13136,13 +13136,13 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="M249" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="N249" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="O249" t="n">
         <v>3</v>
@@ -13175,10 +13175,10 @@
         <v>1.791472319552302</v>
       </c>
       <c r="H250" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -13187,10 +13187,10 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="M250" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="N250" t="n">
         <v>1.25</v>
@@ -13226,10 +13226,10 @@
         <v>1.383934764191501</v>
       </c>
       <c r="H251" t="n">
-        <v>1.480000019073486</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="I251" t="n">
-        <v>1.649999976158142</v>
+        <v>1.629999995231628</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -13238,13 +13238,13 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="M251" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="N251" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="O251" t="n">
         <v>2</v>
@@ -13277,10 +13277,10 @@
         <v>0.705116610974073</v>
       </c>
       <c r="H252" t="n">
-        <v>1.019999980926514</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6399999856948853</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -13289,13 +13289,13 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M252" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="N252" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O252" t="n">
         <v>3</v>
@@ -13328,10 +13328,10 @@
         <v>1.382349655032152</v>
       </c>
       <c r="H253" t="n">
-        <v>0.9700000286102295</v>
+        <v>0.9399999976158142</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -13340,13 +13340,13 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M253" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="N253" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="O253" t="n">
         <v>2</v>
@@ -13379,10 +13379,10 @@
         <v>2.573885659687221</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1099999994039536</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="I254" t="n">
-        <v>2.690000057220459</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -13391,13 +13391,13 @@
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M254" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="N254" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="O254" t="n">
         <v>2</v>
@@ -13430,10 +13430,10 @@
         <v>0.623960616067048</v>
       </c>
       <c r="H255" t="n">
-        <v>0.7599999904632568</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="I255" t="n">
-        <v>0.9900000095367432</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -13442,13 +13442,13 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="M255" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="N255" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -13481,10 +13481,10 @@
         <v>0.75706783868372</v>
       </c>
       <c r="H256" t="n">
-        <v>1.539999961853027</v>
+        <v>1.649999976158142</v>
       </c>
       <c r="I256" t="n">
-        <v>0.5799999833106995</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -13493,13 +13493,13 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="M256" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="N256" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="O256" t="n">
         <v>3</v>
@@ -13532,10 +13532,10 @@
         <v>1.039658511057492</v>
       </c>
       <c r="H257" t="n">
-        <v>0.9900000095367432</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M257" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N257" t="n">
         <v>0.26</v>
@@ -13583,10 +13583,10 @@
         <v>0.5100827524438518</v>
       </c>
       <c r="H258" t="n">
-        <v>2.319999933242798</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -13595,13 +13595,13 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="M258" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="N258" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="O258" t="n">
         <v>1</v>
@@ -13634,7 +13634,7 @@
         <v>0.1457034172490194</v>
       </c>
       <c r="H259" t="n">
-        <v>2.559999942779541</v>
+        <v>2.789999961853027</v>
       </c>
       <c r="I259" t="n">
         <v>0.07999999821186066</v>
@@ -13646,13 +13646,13 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="M259" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N259" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="O259" t="n">
         <v>3</v>
@@ -13685,7 +13685,7 @@
         <v>0.279807333834467</v>
       </c>
       <c r="H260" t="n">
-        <v>1.409999966621399</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I260" t="n">
         <v>0.3700000047683716</v>
@@ -13697,13 +13697,13 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="M260" t="n">
         <v>0.09</v>
       </c>
       <c r="N260" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="O260" t="n">
         <v>1</v>
@@ -13736,10 +13736,10 @@
         <v>0.5999353146180491</v>
       </c>
       <c r="H261" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7900000214576721</v>
       </c>
       <c r="I261" t="n">
-        <v>0.6899999976158142</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -13748,13 +13748,13 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="M261" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="N261" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="O261" t="n">
         <v>1</v>
@@ -13787,10 +13787,10 @@
         <v>0.5643512820824991</v>
       </c>
       <c r="H262" t="n">
-        <v>1.129999995231628</v>
+        <v>1.190000057220459</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6800000071525574</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -13799,13 +13799,13 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="M262" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="N262" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="O262" t="n">
         <v>2</v>
@@ -13838,10 +13838,10 @@
         <v>0.270975988358256</v>
       </c>
       <c r="H263" t="n">
-        <v>2.130000114440918</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1899999976158142</v>
+        <v>0.2099999934434891</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -13850,13 +13850,13 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="M263" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="N263" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="O263" t="n">
         <v>4</v>
@@ -13889,10 +13889,10 @@
         <v>0.6843167338520231</v>
       </c>
       <c r="H264" t="n">
-        <v>0.3499999940395355</v>
+        <v>0.3600000143051147</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -13901,13 +13901,13 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M264" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="N264" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="O264" t="n">
         <v>3</v>
@@ -13940,10 +13940,10 @@
         <v>0.208856437355279</v>
       </c>
       <c r="H265" t="n">
-        <v>1.100000023841858</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3300000131130219</v>
+        <v>0.3400000035762787</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -13952,13 +13952,13 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="M265" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="N265" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="O265" t="n">
         <v>2</v>
@@ -13991,10 +13991,10 @@
         <v>3.635759250726541</v>
       </c>
       <c r="H266" t="n">
-        <v>0.9900000095367432</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="I266" t="n">
-        <v>2.619999885559082</v>
+        <v>2.25</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -14006,10 +14006,10 @@
         <v>0.08</v>
       </c>
       <c r="M266" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="N266" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="O266" t="n">
         <v>2</v>
@@ -14042,10 +14042,10 @@
         <v>3.180252930149421</v>
       </c>
       <c r="H267" t="n">
-        <v>1.120000004768372</v>
+        <v>1.200000047683716</v>
       </c>
       <c r="I267" t="n">
-        <v>3.339999914169312</v>
+        <v>3.279999971389771</v>
       </c>
       <c r="J267" t="n">
         <v>1</v>
@@ -14054,13 +14054,13 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="M267" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="N267" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="O267" t="n">
         <v>2</v>
@@ -14093,10 +14093,10 @@
         <v>1.052850336767737</v>
       </c>
       <c r="H268" t="n">
-        <v>1.049999952316284</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="I268" t="n">
-        <v>1.399999976158142</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -14105,13 +14105,13 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="M268" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="N268" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="O268" t="n">
         <v>2</v>
@@ -14144,10 +14144,10 @@
         <v>1.356821719557043</v>
       </c>
       <c r="H269" t="n">
-        <v>1.590000033378601</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="I269" t="n">
-        <v>1.279999971389771</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -14156,13 +14156,13 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="M269" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="N269" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="O269" t="n">
         <v>6</v>
@@ -14195,10 +14195,10 @@
         <v>0.6354369381442679</v>
       </c>
       <c r="H270" t="n">
-        <v>0.4300000071525574</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="I270" t="n">
-        <v>0.6100000143051147</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -14207,13 +14207,13 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M270" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N270" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O270" t="n">
         <v>1</v>
@@ -14246,10 +14246,10 @@
         <v>0.733843019232151</v>
       </c>
       <c r="H271" t="n">
-        <v>0.7200000286102295</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="I271" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -14258,13 +14258,13 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="M271" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="N271" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O271" t="n">
         <v>3</v>
